--- a/backtest_runs/20260410_193731/by_symbol/NICL/NICL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/NICL/NICL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-3735.830000000001</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>98990.49000000001</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>98990.49000000001</v>
@@ -679,7 +679,7 @@
         <v>-4996.110000000007</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>93994.38</v>
@@ -771,7 +771,7 @@
         <v>-771.6000000000109</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>97370.13</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>97370.13</v>
@@ -909,7 +909,7 @@
         <v>-1575.349999999993</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>95794.78</v>
@@ -955,7 +955,7 @@
         <v>-6738.639999999993</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>89056.14000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-1125.25</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>91846.76000000001</v>
@@ -1139,7 +1139,7 @@
         <v>-1138.110000000006</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>90708.65000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-1350.299999999996</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>89358.35000000001</v>
@@ -1415,7 +1415,7 @@
         <v>-1195.97999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91692.44000000002</v>
@@ -1461,7 +1461,7 @@
         <v>-945.2099999999992</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>90747.23000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-218.6200000000022</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>99151.24000000001</v>
